--- a/results/Int Task Remove ACC 0.1/Rando_1_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_1_permute.xlsx
@@ -440,87 +440,87 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7416280050102124</v>
+        <v>0.7444199785242098</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7367364649979647</v>
+        <v>0.7439419670519345</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7353108856166559</v>
+        <v>0.7549446859497844</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7346960837483347</v>
+        <v>0.7514533602122939</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7346960837483347</v>
+        <v>0.7466394253474717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.730223369959742</v>
+        <v>0.7466394253474717</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7159775410099418</v>
+        <v>0.7394170132224677</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7178726768280088</v>
+        <v>0.7305392259294198</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7254870402423454</v>
+        <v>0.7172086545743555</v>
       </c>
     </row>
     <row r="11">
@@ -530,497 +530,497 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7254870402423454</v>
+        <v>0.7172086545743555</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7248553283029898</v>
+        <v>0.7192152156819167</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7248553283029898</v>
+        <v>0.721127261571018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7280223430352852</v>
+        <v>0.7180801271637343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7275443315630099</v>
+        <v>0.7164416620667247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7300711793204326</v>
+        <v>0.7129418812937171</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7287823903351698</v>
+        <v>0.7153488487261281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7312331427729376</v>
+        <v>0.7121902890293499</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7317111542452129</v>
+        <v>0.7147086817512553</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7230984927087398</v>
+        <v>0.7151105979038759</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7259496514713574</v>
+        <v>0.7151105979038759</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7248314730242091</v>
+        <v>0.7118843979229601</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.725147328993887</v>
+        <v>0.7135059529489352</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7237471147191298</v>
+        <v>0.7181408222401254</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7229532472771766</v>
+        <v>0.7066770019410346</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7232691032468545</v>
+        <v>0.7200528681292268</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7159029555180582</v>
+        <v>0.7200528681292268</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7184467133465151</v>
+        <v>0.7055588234938864</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7112765412623852</v>
+        <v>0.6876848784105499</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6525333702133931</v>
+        <v>0.6905275821376504</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6436386728493108</v>
+        <v>0.6950087509617603</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6243222383136311</v>
+        <v>0.6385526670201677</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6229389341099082</v>
+        <v>0.6396623904317986</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5824701144691022</v>
+        <v>0.6398245459343962</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5746766854811338</v>
+        <v>0.6398245459343962</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5807117690470813</v>
+        <v>0.6546851767525175</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5732257409932734</v>
+        <v>0.6546851767525175</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.583101826408458</v>
+        <v>0.6542325303867937</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5955216696520994</v>
+        <v>0.6580397120939621</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5952311787889732</v>
+        <v>0.6590633753226502</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5914324521173221</v>
+        <v>0.6456367789213548</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5789941889748753</v>
+        <v>0.6390983187765805</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.569910461173873</v>
+        <v>0.6390983187765805</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5565614699200033</v>
+        <v>0.6483342372168922</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5581745699104612</v>
+        <v>0.6344549944498732</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5471618861493233</v>
+        <v>0.6577069460532499</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5482969746675057</v>
+        <v>0.6604551345618903</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5129694205522587</v>
+        <v>0.5842061144401136</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5794299252695646</v>
+        <v>0.571137649186082</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5941975506969969</v>
+        <v>0.5625334426851261</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6031345232386651</v>
+        <v>0.5566351495152245</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6031345232386651</v>
+        <v>0.543608959438779</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6069670700523849</v>
+        <v>0.5394351915488297</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6099550192110486</v>
+        <v>0.5458114961910064</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6125664173236431</v>
+        <v>0.5400838135592196</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6077086974534641</v>
+        <v>0.5319829836370905</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.630561752559762</v>
+        <v>0.5314457869161948</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6299469506914408</v>
+        <v>0.5188553331344388</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6250385006081587</v>
+        <v>0.5271690487722684</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.607426661625855</v>
+        <v>0.5298580520322885</v>
       </c>
     </row>
     <row r="61">
@@ -1030,137 +1030,137 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6006399857955403</v>
+        <v>0.5277838506405897</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6049336340105012</v>
+        <v>0.5287398735851404</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5978972326668752</v>
+        <v>0.5236354478571921</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5575298734522756</v>
+        <v>0.5242756148320649</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5567106409037708</v>
+        <v>0.5242756148320649</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5386322651402509</v>
+        <v>0.5162086050520045</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5386322651402509</v>
+        <v>0.5183081715502549</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4858843182040539</v>
+        <v>0.5038733121635349</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5283458085369286</v>
+        <v>0.5044712039608218</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5296330876944205</v>
+        <v>0.5052058861541546</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5353692253617245</v>
+        <v>0.5017230154521813</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5353692253617245</v>
+        <v>0.5021925718889395</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5347713335644376</v>
+        <v>0.4945190232259826</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5332766040712204</v>
+        <v>0.4937589759260981</v>
       </c>
     </row>
     <row r="75">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5498010650929027</v>
+        <v>0.4920429056816631</v>
       </c>
     </row>
     <row r="76">
@@ -1180,147 +1180,147 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4933818209489207</v>
+        <v>0.4984460852581624</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5035568522627487</v>
+        <v>0.4979680737858871</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5325210862546488</v>
+        <v>0.4982839297555649</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5325210862546488</v>
+        <v>0.4981302292884846</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5390550169161104</v>
+        <v>0.4981302292884846</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5307413012782806</v>
+        <v>0.4989071866594034</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5318594797254288</v>
+        <v>0.4990947072685525</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5429582236695095</v>
+        <v>0.4940494667892244</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5371873599634742</v>
+        <v>0.4992484077356328</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5368630489582792</v>
+        <v>0.4994105632382303</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5103694971307233</v>
+        <v>0.5021080215337677</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5061872742052569</v>
+        <v>0.5011350885181826</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5063409746723372</v>
+        <v>0.5001790655736319</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5073308177589566</v>
+        <v>0.5003327660407122</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5056908428341762</v>
+        <v>0.5006486220103901</v>
       </c>
     </row>
   </sheetData>
